--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>126372264</v>
       </c>
       <c r="B4" t="n">
-        <v>102484</v>
+        <v>102485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126372639</v>
+        <v>126372262</v>
       </c>
       <c r="B8" t="n">
-        <v>57653</v>
+        <v>109176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,46 +1340,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708007</v>
+        <v>707859</v>
       </c>
       <c r="R8" t="n">
-        <v>6364884</v>
+        <v>6364553</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,11 +1400,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1547,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126372262</v>
+        <v>126372639</v>
       </c>
       <c r="B10" t="n">
-        <v>109176</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,37 +1544,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707859</v>
+        <v>708007</v>
       </c>
       <c r="R10" t="n">
-        <v>6364553</v>
+        <v>6364884</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126372489</v>
+        <v>126372643</v>
       </c>
       <c r="B11" t="n">
-        <v>43227</v>
+        <v>57653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,19 +1682,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1703,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707981</v>
+        <v>708011</v>
       </c>
       <c r="R11" t="n">
-        <v>6364809</v>
+        <v>6364863</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nyutkläckt fräsch.</t>
+          <t>Granlåga med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,7 +1747,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1775,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126372643</v>
+        <v>126372489</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>43227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1808,9 +1798,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708011</v>
+        <v>707981</v>
       </c>
       <c r="R12" t="n">
-        <v>6364863</v>
+        <v>6364809</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Granlåga med spillkråkehack för födosök.</t>
+          <t>Nyutkläckt fräsch.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126372262</v>
+        <v>126372639</v>
       </c>
       <c r="B8" t="n">
-        <v>109176</v>
+        <v>57653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,37 +1340,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707859</v>
+        <v>708007</v>
       </c>
       <c r="R8" t="n">
-        <v>6364553</v>
+        <v>6364884</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126372639</v>
+        <v>126372262</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>109176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,46 +1558,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708007</v>
+        <v>707859</v>
       </c>
       <c r="R10" t="n">
-        <v>6364884</v>
+        <v>6364553</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126372643</v>
+        <v>126372489</v>
       </c>
       <c r="B11" t="n">
-        <v>57653</v>
+        <v>43227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,9 +1682,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1693,13 +1703,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708011</v>
+        <v>707981</v>
       </c>
       <c r="R11" t="n">
-        <v>6364863</v>
+        <v>6364809</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1743,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Granlåga med spillkråkehack för födosök.</t>
+          <t>Nyutkläckt fräsch.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,7 +1757,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1765,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126372489</v>
+        <v>126372643</v>
       </c>
       <c r="B12" t="n">
-        <v>43227</v>
+        <v>57653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1798,19 +1808,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707981</v>
+        <v>708011</v>
       </c>
       <c r="R12" t="n">
-        <v>6364809</v>
+        <v>6364863</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Nyutkläckt fräsch.</t>
+          <t>Granlåga med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126372649</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126372259</v>
       </c>
       <c r="B3" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>126372264</v>
       </c>
       <c r="B4" t="n">
-        <v>102485</v>
+        <v>102494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>126372271</v>
       </c>
       <c r="B5" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126372326</v>
       </c>
       <c r="B6" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>126372270</v>
       </c>
       <c r="B7" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126372639</v>
+        <v>126372262</v>
       </c>
       <c r="B8" t="n">
-        <v>57653</v>
+        <v>109185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,46 +1340,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708007</v>
+        <v>707859</v>
       </c>
       <c r="R8" t="n">
-        <v>6364884</v>
+        <v>6364553</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,11 +1400,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1434,7 @@
         <v>126372269</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126372262</v>
+        <v>126372639</v>
       </c>
       <c r="B10" t="n">
-        <v>109176</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,37 +1544,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707859</v>
+        <v>708007</v>
       </c>
       <c r="R10" t="n">
-        <v>6364553</v>
+        <v>6364884</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126372489</v>
+        <v>126372643</v>
       </c>
       <c r="B11" t="n">
-        <v>43227</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,19 +1682,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1703,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707981</v>
+        <v>708011</v>
       </c>
       <c r="R11" t="n">
-        <v>6364809</v>
+        <v>6364863</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nyutkläckt fräsch.</t>
+          <t>Granlåga med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,7 +1747,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med lundstarr.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1775,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126372643</v>
+        <v>126372489</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>43228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1808,9 +1798,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708011</v>
+        <v>707981</v>
       </c>
       <c r="R12" t="n">
-        <v>6364863</v>
+        <v>6364809</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Granlåga med spillkråkehack för födosök.</t>
+          <t>Nyutkläckt fräsch.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126372262</v>
+        <v>126372639</v>
       </c>
       <c r="B8" t="n">
-        <v>109185</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,37 +1340,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707859</v>
+        <v>708007</v>
       </c>
       <c r="R8" t="n">
-        <v>6364553</v>
+        <v>6364884</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126372269</v>
+        <v>126372262</v>
       </c>
       <c r="B9" t="n">
         <v>109185</v>
@@ -1466,13 +1480,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707854</v>
+        <v>707859</v>
       </c>
       <c r="R9" t="n">
-        <v>6364556</v>
+        <v>6364553</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126372639</v>
+        <v>126372269</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>109185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,46 +1558,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708007</v>
+        <v>707854</v>
       </c>
       <c r="R10" t="n">
-        <v>6364884</v>
+        <v>6364556</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1889,6 +1889,2085 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126521656</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98397</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>707885</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6364864</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126521646</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98253</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219769</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vit skogslilja</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cephalanthera longifolia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Fritsch</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>707828</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6364928</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126521613</v>
+      </c>
+      <c r="B15" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>707840</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6364558</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126521635</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>707704</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6364742</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126521703</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>707905</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6364636</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126521634</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>707704</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6364742</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126521684</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>707803</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6364747</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126521702</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>707879</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6364637</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126521627</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>707757</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6364667</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126521643</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>707800</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6364900</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126521617</v>
+      </c>
+      <c r="B23" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>707850</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6364575</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126521626</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>707757</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6364667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126521619</v>
+      </c>
+      <c r="B25" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>707841</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6364587</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126521691</v>
+      </c>
+      <c r="B26" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>707798</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6364637</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126521630</v>
+      </c>
+      <c r="B27" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>707739</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6364690</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126521685</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>707796</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6364706</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126521704</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>707905</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6364627</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126521616</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>707850</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6364575</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126521655</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98397</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>707897</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6364868</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126521656</v>
+        <v>126521646</v>
       </c>
       <c r="B13" t="n">
-        <v>98397</v>
+        <v>98253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,26 +1902,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223621</v>
+        <v>219769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707885</v>
+        <v>707828</v>
       </c>
       <c r="R13" t="n">
-        <v>6364864</v>
+        <v>6364928</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126521646</v>
+        <v>126521656</v>
       </c>
       <c r="B14" t="n">
-        <v>98253</v>
+        <v>98397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,26 +2013,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219769</v>
+        <v>223621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707828</v>
+        <v>707885</v>
       </c>
       <c r="R14" t="n">
-        <v>6364928</v>
+        <v>6364864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126521703</v>
+        <v>126521634</v>
       </c>
       <c r="B17" t="n">
         <v>98384</v>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2370,13 +2370,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707905</v>
+        <v>707704</v>
       </c>
       <c r="R17" t="n">
-        <v>6364636</v>
+        <v>6364742</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126521634</v>
+        <v>126521703</v>
       </c>
       <c r="B18" t="n">
         <v>98384</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2481,13 +2481,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707704</v>
+        <v>707905</v>
       </c>
       <c r="R18" t="n">
-        <v>6364742</v>
+        <v>6364636</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126521684</v>
+        <v>126521702</v>
       </c>
       <c r="B19" t="n">
         <v>98384</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707803</v>
+        <v>707879</v>
       </c>
       <c r="R19" t="n">
-        <v>6364747</v>
+        <v>6364637</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126521702</v>
+        <v>126521684</v>
       </c>
       <c r="B20" t="n">
         <v>98384</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707879</v>
+        <v>707803</v>
       </c>
       <c r="R20" t="n">
-        <v>6364637</v>
+        <v>6364747</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3303,45 +3303,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126521691</v>
+        <v>126521685</v>
       </c>
       <c r="B26" t="n">
-        <v>109185</v>
+        <v>98384</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707798</v>
+        <v>707796</v>
       </c>
       <c r="R26" t="n">
-        <v>6364637</v>
+        <v>6364706</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3374,11 +3383,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,54 +3530,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126521685</v>
+        <v>126521691</v>
       </c>
       <c r="B28" t="n">
-        <v>98384</v>
+        <v>109185</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707796</v>
+        <v>707798</v>
       </c>
       <c r="R28" t="n">
-        <v>6364706</v>
+        <v>6364637</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3606,6 +3601,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,10 +3637,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126521704</v>
+        <v>126521616</v>
       </c>
       <c r="B29" t="n">
-        <v>98384</v>
+        <v>105396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,26 +3648,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707905</v>
+        <v>707850</v>
       </c>
       <c r="R29" t="n">
-        <v>6364627</v>
+        <v>6364575</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126521616</v>
+        <v>126521704</v>
       </c>
       <c r="B30" t="n">
-        <v>105396</v>
+        <v>98384</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,26 +3759,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707850</v>
+        <v>707905</v>
       </c>
       <c r="R30" t="n">
-        <v>6364575</v>
+        <v>6364627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126372639</v>
+        <v>126372262</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>109185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,46 +1340,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708007</v>
+        <v>707859</v>
       </c>
       <c r="R8" t="n">
-        <v>6364884</v>
+        <v>6364553</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,11 +1400,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,7 +1431,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126372262</v>
+        <v>126372269</v>
       </c>
       <c r="B9" t="n">
         <v>109185</v>
@@ -1480,13 +1466,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>707859</v>
+        <v>707854</v>
       </c>
       <c r="R9" t="n">
-        <v>6364553</v>
+        <v>6364556</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126372269</v>
+        <v>126372639</v>
       </c>
       <c r="B10" t="n">
-        <v>109185</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,37 +1544,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707854</v>
+        <v>708007</v>
       </c>
       <c r="R10" t="n">
-        <v>6364556</v>
+        <v>6364884</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,6 +1613,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Tall, död, stående med spillkråkehack för födosök.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3637,10 +3637,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126521616</v>
+        <v>126521704</v>
       </c>
       <c r="B29" t="n">
-        <v>105396</v>
+        <v>98384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,26 +3648,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707850</v>
+        <v>707905</v>
       </c>
       <c r="R29" t="n">
-        <v>6364575</v>
+        <v>6364627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126521704</v>
+        <v>126521616</v>
       </c>
       <c r="B30" t="n">
-        <v>98384</v>
+        <v>105396</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,26 +3759,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707905</v>
+        <v>707850</v>
       </c>
       <c r="R30" t="n">
-        <v>6364627</v>
+        <v>6364575</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3968,6 +3968,1394 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126595160</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>707777</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6364671</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126595159</v>
+      </c>
+      <c r="B33" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>707777</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6364671</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126595185</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>707765</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6364880</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126595189</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>707857</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6364590</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126595364</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>707800</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6364840</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126595158</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98336</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>707816</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6364869</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126595186</v>
+      </c>
+      <c r="B38" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>707793</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6364879</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126595152</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99578</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>174</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Strävlosta</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bromopsis benekenii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>707740</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6364620</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126595154</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>707707</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6364741</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Vid skogsek med snitsel.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126595188</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>707796</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6364640</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126595187</v>
+      </c>
+      <c r="B42" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>707837</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6364631</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126595153</v>
+      </c>
+      <c r="B43" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>707723</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6364659</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -3637,10 +3637,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126521704</v>
+        <v>126521616</v>
       </c>
       <c r="B29" t="n">
-        <v>98384</v>
+        <v>105396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,26 +3648,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707905</v>
+        <v>707850</v>
       </c>
       <c r="R29" t="n">
-        <v>6364627</v>
+        <v>6364575</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126521616</v>
+        <v>126521704</v>
       </c>
       <c r="B30" t="n">
-        <v>105396</v>
+        <v>98384</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3759,26 +3759,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707850</v>
+        <v>707905</v>
       </c>
       <c r="R30" t="n">
-        <v>6364575</v>
+        <v>6364627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -3970,44 +3970,35 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126595160</v>
+        <v>126595159</v>
       </c>
       <c r="B32" t="n">
-        <v>98339</v>
+        <v>109260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
@@ -4081,35 +4072,44 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126595159</v>
+        <v>126595160</v>
       </c>
       <c r="B33" t="n">
-        <v>109185</v>
+        <v>98414</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
@@ -4549,7 +4549,7 @@
         <v>126595158</v>
       </c>
       <c r="B37" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>126595152</v>
       </c>
       <c r="B38" t="n">
-        <v>99578</v>
+        <v>99653</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>126595154</v>
       </c>
       <c r="B40" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126595153</v>
       </c>
       <c r="B43" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,27 +5358,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126706390</v>
+        <v>126706392</v>
       </c>
       <c r="B44" t="n">
-        <v>58300</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103042</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5386,14 +5386,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5402,10 +5398,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707885</v>
+        <v>707868</v>
       </c>
       <c r="R44" t="n">
-        <v>6364864</v>
+        <v>6364637</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5438,6 +5434,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillkråkebo f.d. i gammal tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5464,27 +5465,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126706392</v>
+        <v>126706390</v>
       </c>
       <c r="B45" t="n">
-        <v>57654</v>
+        <v>58300</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5492,10 +5493,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5504,10 +5509,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707868</v>
+        <v>707885</v>
       </c>
       <c r="R45" t="n">
-        <v>6364637</v>
+        <v>6364864</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5540,11 +5545,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spillkråkebo f.d. i gammal tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 24309-2025 artfynd.xlsx
+++ b/artfynd/A 24309-2025 artfynd.xlsx
@@ -3970,35 +3970,44 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126595159</v>
+        <v>126595160</v>
       </c>
       <c r="B32" t="n">
-        <v>109260</v>
+        <v>98420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
@@ -4072,44 +4081,35 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126595160</v>
+        <v>126595159</v>
       </c>
       <c r="B33" t="n">
-        <v>98414</v>
+        <v>109266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lojsthajd 1:1., Gtl</t>
@@ -4549,7 +4549,7 @@
         <v>126595158</v>
       </c>
       <c r="B37" t="n">
-        <v>98411</v>
+        <v>98417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>126595152</v>
       </c>
       <c r="B38" t="n">
-        <v>99653</v>
+        <v>99659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>126595154</v>
       </c>
       <c r="B40" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126595153</v>
       </c>
       <c r="B43" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
